--- a/seed_kits/legacy_wrangling_v2/raw/Unique_injected_rna__preview_dqm.xlsx
+++ b/seed_kits/legacy_wrangling_v2/raw/Unique_injected_rna__preview_dqm.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,7 +834,11 @@
           <t>phiC-NLS</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>pDQM112</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -937,6 +941,30 @@
       <c r="B46" t="inlineStr">
         <is>
           <t>pDQM047</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>phiC-NLS, 2xLynk:mSG</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>pDQM112, pDQM047</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>phiC-NLS, 2xLynk:mSG, mChilada:H2B</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>pDQM112, pDQM047, pDQM104</t>
         </is>
       </c>
     </row>
